--- a/artfynd/A 60091-2024 artfynd.xlsx
+++ b/artfynd/A 60091-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114569709</v>
+        <v>114569713</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>822500</v>
+        <v>822237</v>
       </c>
       <c r="R2" t="n">
-        <v>7302255</v>
+        <v>7302253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,16 +779,11 @@
         <v>114569724</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114569726</v>
+        <v>114569709</v>
       </c>
       <c r="B4" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>822491</v>
+        <v>822500</v>
       </c>
       <c r="R4" t="n">
-        <v>7302477</v>
+        <v>7302255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,112 +975,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>114569713</v>
-      </c>
-      <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Norrbotten, Nb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>822237</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7302253</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Luleå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Nederluleå</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB, Ursula Zinko, Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60091-2024 artfynd.xlsx
+++ b/artfynd/A 60091-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569713</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569724</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569709</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>